--- a/release/RoadX_v2.2_Professional/Sample_BOQ_Estimate.xlsx
+++ b/release/RoadX_v2.2_Professional/Sample_BOQ_Estimate.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Option C (Cost Optimized)</t>
+          <t>Option B (Cost Optimized)</t>
         </is>
       </c>
     </row>
